--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AA99E3-DDD8-43B7-9041-FAC232C996DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CCF0F2-D822-4126-B1B0-85F776D45DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4870" yWindow="790" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttribute" sheetId="2" r:id="rId1"/>
@@ -671,22 +671,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>1200</v>
+        <v>70</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
         <v>60000</v>
@@ -704,22 +704,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>1300</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2">
         <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
         <v>60000</v>
@@ -856,22 +856,22 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>2200</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
       </c>
       <c r="F4" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
         <v>60000</v>
@@ -888,22 +888,22 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>2400</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2">
         <v>10</v>
       </c>
       <c r="F5" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
         <v>60000</v>

--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CCF0F2-D822-4126-B1B0-85F776D45DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515D9D16-30EC-4B89-98FB-2DF4371FF282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4870" yWindow="790" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttribute" sheetId="2" r:id="rId1"/>
@@ -680,7 +680,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H4" s="2">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H5" s="2">
         <v>0</v>

--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{515D9D16-30EC-4B89-98FB-2DF4371FF282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCF7F13-D03B-43F6-A238-942E3C4CE923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5210" yWindow="1130" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttribute" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -96,6 +96,10 @@
   </si>
   <si>
     <t>攻击速度</t>
+  </si>
+  <si>
+    <t>AttackSpeed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -556,6 +560,7 @@
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.81640625" customWidth="1"/>
     <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -591,7 +596,7 @@
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -626,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -671,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
@@ -692,7 +697,7 @@
         <v>60000</v>
       </c>
       <c r="K4" s="2">
-        <v>1</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -704,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="E5" s="2">
         <v>10</v>
@@ -725,7 +730,7 @@
         <v>60000</v>
       </c>
       <c r="K5" s="2">
-        <v>1</v>
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -811,7 +816,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -856,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
@@ -877,7 +882,7 @@
         <v>60000</v>
       </c>
       <c r="K4" s="2">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -888,7 +893,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E5" s="2">
         <v>10</v>
@@ -909,7 +914,7 @@
         <v>60000</v>
       </c>
       <c r="K5" s="2">
-        <v>1</v>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCF7F13-D03B-43F6-A238-942E3C4CE923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FA3483-8485-4A25-B738-510EBFE7427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5210" yWindow="1130" windowWidth="19200" windowHeight="9970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HeroAttribute" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,50 @@
   </si>
   <si>
     <t>AttackSpeed</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前最大经验</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxExp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>名称</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>炼气</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>筑基</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>金丹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>元婴</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>年龄</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxAge</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -555,16 +599,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" customWidth="1"/>
-    <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.36328125" customWidth="1"/>
+    <col min="11" max="11" width="12.81640625" customWidth="1"/>
+    <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -574,32 +620,39 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3"/>
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="M1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
@@ -609,9 +662,7 @@
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="D2" s="3"/>
       <c r="E2" s="5" t="s">
         <v>14</v>
       </c>
@@ -628,13 +679,22 @@
         <v>14</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -642,32 +702,41 @@
         <v>5</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="F3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>1001</v>
@@ -675,32 +744,41 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2">
         <v>200</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>10</v>
       </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
       <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
         <v>1000</v>
       </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
       <c r="I4" s="2">
         <v>0</v>
       </c>
       <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
         <v>60000</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="2">
         <v>2000</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="M4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N4" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>1001</v>
@@ -708,30 +786,124 @@
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2">
         <v>320</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="2">
         <v>10</v>
       </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
       <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
         <v>1000</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
         <v>60000</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="2">
         <v>2000</v>
       </c>
+      <c r="M5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="N5" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.35">
+      <c r="B6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2">
+        <v>520</v>
+      </c>
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M6" s="2">
+        <v>30000</v>
+      </c>
+      <c r="N6" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="N7" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="D8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -742,14 +914,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -783,8 +956,14 @@
       <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L1" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
@@ -818,8 +997,14 @@
       <c r="K2" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -851,8 +1036,14 @@
       <c r="K3" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>2001</v>
@@ -884,8 +1075,14 @@
       <c r="K4" s="2">
         <v>3000</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="L4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M4" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>2001</v>
       </c>
@@ -915,6 +1112,88 @@
       </c>
       <c r="K5" s="2">
         <v>3000</v>
+      </c>
+      <c r="L5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="M5" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.35">
+      <c r="B6" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>150</v>
+      </c>
+      <c r="E6" s="2">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>60000</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3000</v>
+      </c>
+      <c r="L6" s="2">
+        <v>30000</v>
+      </c>
+      <c r="M6" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15" x14ac:dyDescent="0.35">
+      <c r="B7" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>150</v>
+      </c>
+      <c r="E7" s="2">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>60000</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="M7" s="2">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FA3483-8485-4A25-B738-510EBFE7427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DBF28F-E9A1-41B5-9357-3CDEE637BDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>MoveSpeed</t>
-  </si>
-  <si>
-    <t>AttackSpeed</t>
   </si>
   <si>
     <t>##type</t>
@@ -102,10 +99,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>当前最大经验</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>long</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -114,26 +107,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>名称</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>炼气</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>筑基</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>金丹</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>元婴</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -143,6 +116,22 @@
   </si>
   <si>
     <t>MaxAge</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SubLevel</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>NextExp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前最大等级经验</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个等级经验</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -248,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -271,6 +260,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -282,7 +280,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -292,6 +290,18 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="差" xfId="3" builtinId="27"/>
@@ -599,311 +609,697 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.81640625" customWidth="1"/>
     <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.90625" customWidth="1"/>
+    <col min="13" max="13" width="11.7265625" customWidth="1"/>
+    <col min="14" max="14" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="5" t="s">
+      <c r="D1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="2"/>
-      <c r="B4" s="1">
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10">
         <v>1001</v>
       </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="C4" s="10">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="9">
         <v>200</v>
       </c>
-      <c r="F4" s="2">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="2">
-        <v>60000</v>
-      </c>
-      <c r="L4" s="2">
-        <v>2000</v>
-      </c>
-      <c r="M4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="N4" s="2">
+      <c r="F4" s="9">
+        <v>10</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L4" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M4" s="9">
+        <v>300</v>
+      </c>
+      <c r="N4" s="9">
+        <v>1000</v>
+      </c>
+      <c r="O4" s="9">
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-      <c r="B5" s="1">
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10">
         <v>1001</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="10">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="E5" s="9">
+        <v>210</v>
+      </c>
+      <c r="F5" s="9">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9">
+        <v>0</v>
+      </c>
+      <c r="K5" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L5" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M5" s="9">
+        <v>600</v>
+      </c>
+      <c r="N5" s="9">
+        <v>1000</v>
+      </c>
+      <c r="O5" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9">
+        <v>220</v>
+      </c>
+      <c r="F6" s="9">
+        <v>10</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L6" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M6" s="9">
+        <v>1000</v>
+      </c>
+      <c r="N6" s="9">
+        <v>1000</v>
+      </c>
+      <c r="O6" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
         <v>320</v>
       </c>
-      <c r="F5" s="2">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0</v>
-      </c>
-      <c r="H5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>60000</v>
-      </c>
-      <c r="L5" s="2">
-        <v>2000</v>
-      </c>
-      <c r="M5" s="2">
+      <c r="F7" s="9">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L7" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M7" s="9">
+        <v>3000</v>
+      </c>
+      <c r="N7" s="9">
         <v>10000</v>
       </c>
-      <c r="N5" s="2">
+      <c r="O7" s="9">
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" x14ac:dyDescent="0.35">
-      <c r="B6" s="1">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10">
         <v>1001</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>350</v>
+      </c>
+      <c r="F8" s="9">
+        <v>10</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L8" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M8" s="9">
+        <v>6000</v>
+      </c>
+      <c r="N8" s="9">
+        <v>10000</v>
+      </c>
+      <c r="O8" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="10">
         <v>2</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="E9" s="9">
+        <v>380</v>
+      </c>
+      <c r="F9" s="9">
+        <v>10</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L9" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M9" s="9">
+        <v>10000</v>
+      </c>
+      <c r="N9" s="9">
+        <v>10000</v>
+      </c>
+      <c r="O9" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A10" s="11"/>
+      <c r="B10" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
         <v>520</v>
       </c>
-      <c r="F6" s="2">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0</v>
-      </c>
-      <c r="H6" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>60000</v>
-      </c>
-      <c r="L6" s="2">
-        <v>2000</v>
-      </c>
-      <c r="M6" s="2">
+      <c r="F10" s="9">
+        <v>10</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L10" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M10" s="9">
+        <v>15000</v>
+      </c>
+      <c r="N10" s="9">
         <v>30000</v>
       </c>
-      <c r="N6" s="2">
+      <c r="O10" s="9">
         <v>500</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="15" x14ac:dyDescent="0.35">
-      <c r="B7" s="1">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A11" s="11"/>
+      <c r="B11" s="10">
         <v>1001</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C11" s="10">
+        <v>2</v>
+      </c>
+      <c r="D11" s="10">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9">
+        <v>550</v>
+      </c>
+      <c r="F11" s="9">
+        <v>10</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L11" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M11" s="9">
+        <v>20000</v>
+      </c>
+      <c r="N11" s="9">
+        <v>30000</v>
+      </c>
+      <c r="O11" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A12" s="11"/>
+      <c r="B12" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2</v>
+      </c>
+      <c r="D12" s="10">
+        <v>2</v>
+      </c>
+      <c r="E12" s="9">
+        <v>580</v>
+      </c>
+      <c r="F12" s="9">
+        <v>10</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L12" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M12" s="9">
+        <v>30000</v>
+      </c>
+      <c r="N12" s="9">
+        <v>30000</v>
+      </c>
+      <c r="O12" s="9">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A13" s="11"/>
+      <c r="B13" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C13" s="10">
         <v>3</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="2">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>60000</v>
-      </c>
-      <c r="L7" s="2">
-        <v>2000</v>
-      </c>
-      <c r="M7" s="2">
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="9">
+        <v>10</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L13" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M13" s="9">
+        <v>40000</v>
+      </c>
+      <c r="N13" s="9">
         <v>100000</v>
       </c>
-      <c r="N7" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D8" s="1"/>
+      <c r="O13" s="9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A14" s="11"/>
+      <c r="B14" s="10">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="10">
+        <v>3</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="9">
+        <v>10</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L14" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M14" s="9">
+        <v>60000</v>
+      </c>
+      <c r="N14" s="9">
+        <v>100000</v>
+      </c>
+      <c r="O14" s="9">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13">
+        <v>1001</v>
+      </c>
+      <c r="C15" s="13">
+        <v>3</v>
+      </c>
+      <c r="D15" s="13">
+        <v>2</v>
+      </c>
+      <c r="E15" s="14">
+        <v>1500</v>
+      </c>
+      <c r="F15" s="14">
+        <v>10</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="14">
+        <v>0</v>
+      </c>
+      <c r="J15" s="14">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14">
+        <v>60000</v>
+      </c>
+      <c r="L15" s="14">
+        <v>2000</v>
+      </c>
+      <c r="M15" s="14">
+        <v>100000</v>
+      </c>
+      <c r="N15" s="14">
+        <v>100000</v>
+      </c>
+      <c r="O15" s="14">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D16" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -914,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -922,7 +1318,7 @@
     <col min="11" max="11" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -932,118 +1328,134 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="L1" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+        <v>31</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="M2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="3"/>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="I3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="L3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="M3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>2001</v>
@@ -1051,148 +1463,524 @@
       <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>200</v>
+      </c>
+      <c r="F4" s="2">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L4" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M4" s="2">
+        <v>300</v>
+      </c>
+      <c r="N4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O4" s="2">
         <v>100</v>
       </c>
-      <c r="E4" s="2">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>60000</v>
-      </c>
-      <c r="K4" s="2">
-        <v>3000</v>
-      </c>
-      <c r="L4" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M4" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="1">
         <v>2001</v>
       </c>
       <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="2">
-        <v>150</v>
-      </c>
       <c r="E5" s="2">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="F5" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="L5" s="2">
-        <v>10000</v>
+        <v>2000</v>
       </c>
       <c r="M5" s="2">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" x14ac:dyDescent="0.35">
+        <v>600</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O5" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="B6" s="1">
         <v>2001</v>
       </c>
       <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="2">
-        <v>150</v>
-      </c>
       <c r="E6" s="2">
-        <v>10</v>
+        <v>220</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="K6" s="2">
-        <v>3000</v>
+        <v>60000</v>
       </c>
       <c r="L6" s="2">
-        <v>30000</v>
+        <v>2000</v>
       </c>
       <c r="M6" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15" x14ac:dyDescent="0.35">
+        <v>1000</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.35">
       <c r="B7" s="1">
         <v>2001</v>
       </c>
       <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <v>320</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M7" s="2">
+        <v>3000</v>
+      </c>
+      <c r="N7" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O7" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B8" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>350</v>
+      </c>
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M8" s="2">
+        <v>6000</v>
+      </c>
+      <c r="N8" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O8" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B9" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>380</v>
+      </c>
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="N9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="O9" s="2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B10" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
+        <v>520</v>
+      </c>
+      <c r="F10" s="2">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M10" s="2">
+        <v>15000</v>
+      </c>
+      <c r="N10" s="2">
+        <v>30000</v>
+      </c>
+      <c r="O10" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B11" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>550</v>
+      </c>
+      <c r="F11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M11" s="2">
+        <v>20000</v>
+      </c>
+      <c r="N11" s="2">
+        <v>30000</v>
+      </c>
+      <c r="O11" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B12" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>580</v>
+      </c>
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M12" s="2">
+        <v>30000</v>
+      </c>
+      <c r="N12" s="2">
+        <v>30000</v>
+      </c>
+      <c r="O12" s="2">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B13" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="2">
-        <v>150</v>
-      </c>
-      <c r="E7" s="2">
-        <v>10</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1000</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>60000</v>
-      </c>
-      <c r="K7" s="2">
-        <v>3000</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M13" s="2">
+        <v>40000</v>
+      </c>
+      <c r="N13" s="2">
         <v>100000</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O13" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B14" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1200</v>
+      </c>
+      <c r="F14" s="2">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M14" s="2">
+        <v>60000</v>
+      </c>
+      <c r="N14" s="2">
+        <v>100000</v>
+      </c>
+      <c r="O14" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.35">
+      <c r="B15" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F15" s="2">
+        <v>10</v>
+      </c>
+      <c r="G15" s="2">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>0</v>
+      </c>
+      <c r="K15" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L15" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M15" s="2">
+        <v>100000</v>
+      </c>
+      <c r="N15" s="2">
+        <v>100000</v>
+      </c>
+      <c r="O15" s="2">
         <v>1000</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DBF28F-E9A1-41B5-9357-3CDEE637BDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010A7EFF-EB6F-4E91-A1C2-718E3758E1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -280,7 +280,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -290,13 +290,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -609,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
@@ -625,46 +618,46 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -672,46 +665,46 @@
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -719,587 +712,579 @@
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="5" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
         <v>1001</v>
       </c>
-      <c r="C4" s="10">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
         <v>200</v>
       </c>
-      <c r="F4" s="9">
-        <v>10</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0</v>
-      </c>
-      <c r="H4" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0</v>
-      </c>
-      <c r="K4" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L4" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M4" s="9">
+      <c r="F4" s="2">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L4" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M4" s="2">
         <v>300</v>
       </c>
-      <c r="N4" s="9">
-        <v>1000</v>
-      </c>
-      <c r="O4" s="9">
+      <c r="N4" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O4" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1">
         <v>1001</v>
       </c>
-      <c r="C5" s="10">
-        <v>0</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="2">
         <v>210</v>
       </c>
-      <c r="F5" s="9">
-        <v>10</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9">
-        <v>0</v>
-      </c>
-      <c r="K5" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L5" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M5" s="9">
+      <c r="F5" s="2">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0</v>
+      </c>
+      <c r="K5" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M5" s="2">
         <v>600</v>
       </c>
-      <c r="N5" s="9">
-        <v>1000</v>
-      </c>
-      <c r="O5" s="9">
+      <c r="N5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O5" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10">
+      <c r="A6" s="2"/>
+      <c r="B6" s="1">
         <v>1001</v>
       </c>
-      <c r="C6" s="10">
-        <v>0</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="2">
         <v>220</v>
       </c>
-      <c r="F6" s="9">
-        <v>10</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9">
-        <v>0</v>
-      </c>
-      <c r="K6" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L6" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M6" s="9">
-        <v>1000</v>
-      </c>
-      <c r="N6" s="9">
-        <v>1000</v>
-      </c>
-      <c r="O6" s="9">
+      <c r="F6" s="2">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1000</v>
+      </c>
+      <c r="O6" s="2">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
-      <c r="B7" s="10">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
         <v>1001</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
         <v>320</v>
       </c>
-      <c r="F7" s="9">
-        <v>10</v>
-      </c>
-      <c r="G7" s="9">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0</v>
-      </c>
-      <c r="J7" s="9">
-        <v>0</v>
-      </c>
-      <c r="K7" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L7" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M7" s="9">
+      <c r="F7" s="2">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M7" s="2">
         <v>3000</v>
       </c>
-      <c r="N7" s="9">
+      <c r="N7" s="2">
         <v>10000</v>
       </c>
-      <c r="O7" s="9">
+      <c r="O7" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="9"/>
-      <c r="B8" s="10">
+      <c r="A8" s="2"/>
+      <c r="B8" s="1">
         <v>1001</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="1">
         <v>1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="2">
         <v>350</v>
       </c>
-      <c r="F8" s="9">
-        <v>10</v>
-      </c>
-      <c r="G8" s="9">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I8" s="9">
-        <v>0</v>
-      </c>
-      <c r="J8" s="9">
-        <v>0</v>
-      </c>
-      <c r="K8" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L8" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M8" s="9">
+      <c r="F8" s="2">
+        <v>10</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M8" s="2">
         <v>6000</v>
       </c>
-      <c r="N8" s="9">
+      <c r="N8" s="2">
         <v>10000</v>
       </c>
-      <c r="O8" s="9">
+      <c r="O8" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1">
         <v>1001</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="1">
         <v>1</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="1">
         <v>2</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="2">
         <v>380</v>
       </c>
-      <c r="F9" s="9">
-        <v>10</v>
-      </c>
-      <c r="G9" s="9">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I9" s="9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L9" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M9" s="9">
+      <c r="F9" s="2">
+        <v>10</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M9" s="2">
         <v>10000</v>
       </c>
-      <c r="N9" s="9">
+      <c r="N9" s="2">
         <v>10000</v>
       </c>
-      <c r="O9" s="9">
+      <c r="O9" s="2">
         <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="10">
+      <c r="B10" s="1">
         <v>1001</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="1">
         <v>2</v>
       </c>
-      <c r="D10" s="10">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2">
         <v>520</v>
       </c>
-      <c r="F10" s="9">
-        <v>10</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L10" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M10" s="9">
+      <c r="F10" s="2">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M10" s="2">
         <v>15000</v>
       </c>
-      <c r="N10" s="9">
+      <c r="N10" s="2">
         <v>30000</v>
       </c>
-      <c r="O10" s="9">
+      <c r="O10" s="2">
         <v>500</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="10">
+      <c r="B11" s="1">
         <v>1001</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="2">
         <v>550</v>
       </c>
-      <c r="F11" s="9">
-        <v>10</v>
-      </c>
-      <c r="G11" s="9">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L11" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M11" s="9">
+      <c r="F11" s="2">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M11" s="2">
         <v>20000</v>
       </c>
-      <c r="N11" s="9">
+      <c r="N11" s="2">
         <v>30000</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="2">
         <v>500</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.35">
-      <c r="A12" s="11"/>
-      <c r="B12" s="10">
+      <c r="B12" s="1">
         <v>1001</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="2">
         <v>580</v>
       </c>
-      <c r="F12" s="9">
-        <v>10</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L12" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M12" s="9">
+      <c r="F12" s="2">
+        <v>10</v>
+      </c>
+      <c r="G12" s="2">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M12" s="2">
         <v>30000</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="2">
         <v>30000</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="2">
         <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.35">
-      <c r="A13" s="11"/>
-      <c r="B13" s="10">
+      <c r="B13" s="1">
         <v>1001</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="D13" s="10">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9">
-        <v>1000</v>
-      </c>
-      <c r="F13" s="9">
-        <v>10</v>
-      </c>
-      <c r="G13" s="9">
-        <v>0</v>
-      </c>
-      <c r="H13" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I13" s="9">
-        <v>0</v>
-      </c>
-      <c r="J13" s="9">
-        <v>0</v>
-      </c>
-      <c r="K13" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L13" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M13" s="9">
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="2">
+        <v>10</v>
+      </c>
+      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L13" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M13" s="2">
         <v>40000</v>
       </c>
-      <c r="N13" s="9">
+      <c r="N13" s="2">
         <v>100000</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.35">
-      <c r="A14" s="11"/>
-      <c r="B14" s="10">
+      <c r="B14" s="1">
         <v>1001</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="1">
         <v>1</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="2">
         <v>1200</v>
       </c>
-      <c r="F14" s="9">
-        <v>10</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>1000</v>
-      </c>
-      <c r="I14" s="9">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>60000</v>
-      </c>
-      <c r="L14" s="9">
-        <v>2000</v>
-      </c>
-      <c r="M14" s="9">
-        <v>60000</v>
-      </c>
-      <c r="N14" s="9">
+      <c r="F14" s="2">
+        <v>10</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2">
+        <v>60000</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M14" s="2">
+        <v>60000</v>
+      </c>
+      <c r="N14" s="2">
         <v>100000</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="2">
         <v>1000</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.35">
-      <c r="A15" s="12"/>
-      <c r="B15" s="13">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8">
         <v>1001</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="8">
         <v>3</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="8">
         <v>2</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="9">
         <v>1500</v>
       </c>
-      <c r="F15" s="14">
-        <v>10</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>1000</v>
-      </c>
-      <c r="I15" s="14">
-        <v>0</v>
-      </c>
-      <c r="J15" s="14">
-        <v>0</v>
-      </c>
-      <c r="K15" s="14">
-        <v>60000</v>
-      </c>
-      <c r="L15" s="14">
-        <v>2000</v>
-      </c>
-      <c r="M15" s="14">
+      <c r="F15" s="9">
+        <v>10</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>1000</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="9">
+        <v>60000</v>
+      </c>
+      <c r="L15" s="9">
+        <v>2000</v>
+      </c>
+      <c r="M15" s="9">
         <v>100000</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="9">
         <v>100000</v>
       </c>
-      <c r="O15" s="14">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D16" s="1"/>
+      <c r="O15" s="9">
+        <v>1000</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
+++ b/Design/Excel/ET/Datas/Game/UnitConfigAttr.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010A7EFF-EB6F-4E91-A1C2-718E3758E1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667BFB28-56E3-454B-9D4D-DB8475995DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,7 +763,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="F4" s="2">
         <v>10</v>
@@ -808,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>210</v>
+        <v>380</v>
       </c>
       <c r="F5" s="2">
         <v>10</v>
@@ -853,7 +853,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="2">
-        <v>220</v>
+        <v>410</v>
       </c>
       <c r="F6" s="2">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="F7" s="2">
         <v>10</v>
@@ -943,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="F8" s="2">
         <v>10</v>
@@ -988,7 +988,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="F9" s="2">
         <v>10</v>
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>520</v>
+        <v>720</v>
       </c>
       <c r="F10" s="2">
         <v>10</v>
@@ -1076,7 +1076,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="2">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="F11" s="2">
         <v>10</v>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="2">
-        <v>580</v>
+        <v>780</v>
       </c>
       <c r="F12" s="2">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="2">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="F13" s="2">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="2">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="F14" s="2">
         <v>10</v>
